--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">USB_A_SMT_FEMALE</t>
   </si>
   <si>
-    <t xml:space="preserve">C42637</t>
+    <t xml:space="preserve">C668591</t>
   </si>
   <si>
     <t xml:space="preserve">LED5,LED6,LED7,LED8</t>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">R0402</t>
   </si>
   <si>
-    <t xml:space="preserve">C25117</t>
+    <t xml:space="preserve">C25744</t>
   </si>
   <si>
     <t xml:space="preserve">R12</t>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">4K7</t>
   </si>
   <si>
-    <t xml:space="preserve">C23162</t>
+    <t xml:space="preserve">C25900</t>
   </si>
   <si>
     <t xml:space="preserve">RN2</t>
@@ -494,7 +494,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.93"/>
